--- a/tests/perf_v2/perf_history/v2.4.2/multi_label_cls/MULTI_LABEL_CLS-raw-multilabel_small_coco.xlsx
+++ b/tests/perf_v2/perf_history/v2.4.2/multi_label_cls/MULTI_LABEL_CLS-raw-multilabel_small_coco.xlsx
@@ -586,50 +586,50 @@
         <v>79</v>
       </c>
       <c r="C2" t="n">
-        <v>40.74788212776184</v>
+        <v>34.27346515655518</v>
       </c>
       <c r="D2" t="n">
         <v>1.559999942779541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8666666746139526</v>
+        <v>0.8416666388511658</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8133333325386047</v>
+        <v>0.7883333563804626</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.7866666913032532</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.7816666960716248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0490606239041949</v>
+        <v>0.0438673708446417</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0277954284101724</v>
+        <v>0.0155615042895078</v>
       </c>
       <c r="K2" t="n">
-        <v>11.17378401756287</v>
+        <v>10.04104804992676</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0157780790328979</v>
+        <v>0.0145041918754577</v>
       </c>
       <c r="M2" t="n">
-        <v>0.025455093383789</v>
+        <v>0.025184371471405</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0327576661109924</v>
+        <v>0.0333277034759521</v>
       </c>
       <c r="O2" t="n">
-        <v>2.545509338378906</v>
+        <v>2.518437147140503</v>
       </c>
       <c r="P2" t="n">
-        <v>3.275766611099243</v>
+        <v>3.332770347595215</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-125505</t>
+          <t>20250714-172436</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -674,13 +674,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -690,7 +692,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -699,53 +701,53 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C3" t="n">
-        <v>32.73192977905273</v>
+        <v>32.27876949310303</v>
       </c>
       <c r="D3" t="n">
         <v>1.559999942779541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.8166666626930237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8266666531562805</v>
+        <v>0.8050000071525574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8233333230018616</v>
+        <v>0.8016666769981384</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8233333230018616</v>
+        <v>0.7950000166893005</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0475499803433194</v>
+        <v>0.0434347705764544</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0156711768358945</v>
+        <v>0.0159551054239273</v>
       </c>
       <c r="K3" t="n">
-        <v>11.70418429374695</v>
+        <v>10.25971460342407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.018679769039154</v>
+        <v>0.0140705752372741</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0258029794692993</v>
+        <v>0.0246880793571472</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0336549472808837</v>
+        <v>0.0341007041931152</v>
       </c>
       <c r="O3" t="n">
-        <v>2.580297946929932</v>
+        <v>2.468807935714722</v>
       </c>
       <c r="P3" t="n">
-        <v>3.365494728088379</v>
+        <v>3.410070419311523</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-125632</t>
+          <t>20250714-172552</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -790,13 +792,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -806,7 +810,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -815,53 +819,53 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>40.22354435920715</v>
+        <v>26.58599400520325</v>
       </c>
       <c r="D4" t="n">
         <v>1.559999942779541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8083333373069763</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8233333230018616</v>
+        <v>0.8116666674613953</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8233333230018616</v>
+        <v>0.8116666674613953</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8183333277702332</v>
+        <v>0.8016666769981384</v>
       </c>
       <c r="I4" t="n">
-        <v>0.047926433761663</v>
+        <v>0.0442257948472337</v>
       </c>
       <c r="J4" t="n">
-        <v>0.015872212126851</v>
+        <v>0.0162443835288286</v>
       </c>
       <c r="K4" t="n">
-        <v>11.48411059379578</v>
+        <v>10.19732475280762</v>
       </c>
       <c r="L4" t="n">
-        <v>0.016879539489746</v>
+        <v>0.0179567790031433</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0260281014442443</v>
+        <v>0.0252489614486694</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0336520290374755</v>
+        <v>0.0337222623825073</v>
       </c>
       <c r="O4" t="n">
-        <v>2.602810144424438</v>
+        <v>2.524896144866944</v>
       </c>
       <c r="P4" t="n">
-        <v>3.365202903747559</v>
+        <v>3.372226238250732</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-125752</t>
+          <t>20250714-172706</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -906,13 +910,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -922,7 +928,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -931,53 +937,53 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C5" t="n">
-        <v>52.48969960212708</v>
+        <v>42.95795130729675</v>
       </c>
       <c r="D5" t="n">
         <v>1.559999942779541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.824999988079071</v>
+        <v>0.8416666388511658</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8183333277702332</v>
+        <v>0.8149999976158142</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8216666579246521</v>
+        <v>0.8133333325386047</v>
       </c>
       <c r="H5" t="n">
-        <v>0.824999988079071</v>
+        <v>0.8116666674613953</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0470104140874284</v>
+        <v>0.0449724591365365</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0126479435712099</v>
+        <v>0.015798645094037</v>
       </c>
       <c r="K5" t="n">
-        <v>10.16802525520325</v>
+        <v>10.61355447769165</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0161595749855041</v>
+        <v>0.0141185426712036</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0257299661636352</v>
+        <v>0.02433607339859</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0348599171638488</v>
+        <v>0.0339017581939697</v>
       </c>
       <c r="O5" t="n">
-        <v>2.572996616363525</v>
+        <v>2.433607339859009</v>
       </c>
       <c r="P5" t="n">
-        <v>3.485991716384888</v>
+        <v>3.390175819396973</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-125919</t>
+          <t>20250714-172815</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1022,13 +1028,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1038,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1047,53 +1055,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C6" t="n">
-        <v>41.11738872528076</v>
+        <v>32.52994441986084</v>
       </c>
       <c r="D6" t="n">
         <v>1.559999942779541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8083333373069763</v>
+        <v>0.8416666388511658</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8349999785423279</v>
+        <v>0.7933333516120911</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.7950000166893005</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8266666531562805</v>
+        <v>0.7933333516120911</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0478610439768319</v>
+        <v>0.0437907026325528</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0159677322953939</v>
+        <v>0.0122133446857333</v>
       </c>
       <c r="K6" t="n">
-        <v>12.13921785354614</v>
+        <v>10.28611922264099</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0160096788406372</v>
+        <v>0.0144801878929138</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0256028795242309</v>
+        <v>0.0251151418685913</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0333520889282226</v>
+        <v>0.0333800983428955</v>
       </c>
       <c r="O6" t="n">
-        <v>2.560287952423096</v>
+        <v>2.511514186859131</v>
       </c>
       <c r="P6" t="n">
-        <v>3.335208892822266</v>
+        <v>3.338009834289551</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-130056</t>
+          <t>20250714-172940</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1138,13 +1146,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1154,7 +1164,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1321,56 +1331,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>27.75517678260803</v>
+        <v>22.25048875808716</v>
       </c>
       <c r="D2" t="n">
         <v>4.239999771118164</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8083333373069763</v>
+        <v>0.8333333134651184</v>
       </c>
       <c r="F2" t="n">
+        <v>0.8100000023841858</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8066666722297668</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.8116666674613953</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.8100000023841858</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.8100000023841858</v>
-      </c>
       <c r="I2" t="n">
-        <v>0.0766408826623643</v>
+        <v>0.0730128447440537</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0364560335874557</v>
+        <v>0.0344837754964828</v>
       </c>
       <c r="K2" t="n">
-        <v>8.826914548873901</v>
+        <v>7.925144910812378</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0138120555877685</v>
+        <v>0.0135979461669921</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0245128750801086</v>
+        <v>0.0221427130699157</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0284588766098022</v>
+        <v>0.0271416449546813</v>
       </c>
       <c r="O2" t="n">
-        <v>2.451287508010864</v>
+        <v>2.214271306991577</v>
       </c>
       <c r="P2" t="n">
-        <v>2.845887660980225</v>
+        <v>2.71416449546814</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-101729</t>
+          <t>20250714-150317</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -1415,13 +1425,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1431,19 +1443,19 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C3" t="n">
-        <v>29.94252872467041</v>
+        <v>35.33446884155273</v>
       </c>
       <c r="D3" t="n">
         <v>4.239999771118164</v>
@@ -1452,41 +1464,41 @@
         <v>0.824999988079071</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8133333325386047</v>
+        <v>0.7916666865348816</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8116666674613953</v>
+        <v>0.7900000214576721</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8033333420753479</v>
+        <v>0.7816666960716248</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0753073068680586</v>
+        <v>0.07228390585530441</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0377026833593845</v>
+        <v>0.0319138914346694</v>
       </c>
       <c r="K3" t="n">
-        <v>8.945719003677368</v>
+        <v>8.022486448287964</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0129992771148681</v>
+        <v>0.0107755923271179</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0248410010337829</v>
+        <v>0.0248876309394836</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0278049254417419</v>
+        <v>0.0265168666839599</v>
       </c>
       <c r="O3" t="n">
-        <v>2.484100103378296</v>
+        <v>2.488763093948364</v>
       </c>
       <c r="P3" t="n">
-        <v>2.780492544174194</v>
+        <v>2.651686668395996</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-101838</t>
+          <t>20250714-150416</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1531,13 +1543,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1547,19 +1561,19 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>49.51725745201111</v>
+        <v>38.15227437019348</v>
       </c>
       <c r="D4" t="n">
         <v>4.239999771118164</v>
@@ -1568,41 +1582,41 @@
         <v>0.875</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8133333325386047</v>
+        <v>0.8050000071525574</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8066666722297668</v>
+        <v>0.8149999976158142</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8050000071525574</v>
+        <v>0.7983333468437195</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0752500380845145</v>
+        <v>0.0721733884626551</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0339115820825099</v>
+        <v>0.0313628762960433</v>
       </c>
       <c r="K4" t="n">
-        <v>8.485718488693237</v>
+        <v>7.836306810379028</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0134689497947692</v>
+        <v>0.0112775874137878</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0218008685111999</v>
+        <v>0.0216008138656616</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0272869038581848</v>
+        <v>0.0277541995048522</v>
       </c>
       <c r="O4" t="n">
-        <v>2.180086851119995</v>
+        <v>2.160081386566162</v>
       </c>
       <c r="P4" t="n">
-        <v>2.728690385818481</v>
+        <v>2.775419950485229</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-101949</t>
+          <t>20250714-150527</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1647,13 +1661,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1663,19 +1679,19 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
         <v>49</v>
       </c>
       <c r="C5" t="n">
-        <v>28.32524871826172</v>
+        <v>24.7381386756897</v>
       </c>
       <c r="D5" t="n">
         <v>4.239999771118164</v>
@@ -1684,41 +1700,41 @@
         <v>0.8083333373069763</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8033333420753479</v>
+        <v>0.8083333373069763</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8033333420753479</v>
+        <v>0.8116666674613953</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7933333516120911</v>
+        <v>0.79666668176651</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07471274113168511</v>
+        <v>0.0718589439531977</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0340714752674102</v>
+        <v>0.0396920964121818</v>
       </c>
       <c r="K5" t="n">
-        <v>8.546545267105103</v>
+        <v>8.123530149459839</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0132715392112731</v>
+        <v>0.0113037037849426</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0242884516716003</v>
+        <v>0.026767885684967</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0271420907974243</v>
+        <v>0.0281822347640991</v>
       </c>
       <c r="O5" t="n">
-        <v>2.428845167160034</v>
+        <v>2.676788568496704</v>
       </c>
       <c r="P5" t="n">
-        <v>2.714209079742432</v>
+        <v>2.818223476409912</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-102119</t>
+          <t>20250714-150642</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1763,13 +1779,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1779,62 +1797,62 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>25.3164370059967</v>
+        <v>26.54891753196716</v>
       </c>
       <c r="D6" t="n">
         <v>4.239999771118164</v>
       </c>
       <c r="E6" t="n">
+        <v>0.8500000238418579</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.8333333134651184</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.8216666579246521</v>
-      </c>
       <c r="G6" t="n">
-        <v>0.8216666579246521</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8216666579246521</v>
+        <v>0.8199999928474426</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0751132445240562</v>
+        <v>0.0717796557755381</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0375187955796718</v>
+        <v>0.0318790152668952</v>
       </c>
       <c r="K6" t="n">
-        <v>9.214349746704102</v>
+        <v>7.895124673843384</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0156664752960205</v>
+        <v>0.0112169981002807</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0213436484336853</v>
+        <v>0.0239215064048767</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0271522831916809</v>
+        <v>0.0277015900611877</v>
       </c>
       <c r="O6" t="n">
-        <v>2.13436484336853</v>
+        <v>2.392150640487671</v>
       </c>
       <c r="P6" t="n">
-        <v>2.715228319168091</v>
+        <v>2.770159006118774</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-101621</t>
+          <t>20250714-150744</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1859,7 +1877,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1879,13 +1897,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1895,7 +1915,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2065,53 +2085,53 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="C2" t="n">
-        <v>91.19117665290833</v>
+        <v>107.4904181957245</v>
       </c>
       <c r="D2" t="n">
-        <v>5.690000057220459</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.8916666507720947</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.8483333587646484</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8349999785423279</v>
+        <v>0.8366666436195374</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8216666579246521</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1108831153320731</v>
+        <v>0.1018290887248582</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0460867583751678</v>
+        <v>0.0451197326183319</v>
       </c>
       <c r="K2" t="n">
-        <v>20.87897849082947</v>
+        <v>18.87852907180786</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0251807427406311</v>
+        <v>0.0363155937194824</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0346922183036804</v>
+        <v>0.0316173005104064</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0470363593101501</v>
+        <v>0.0407926869392395</v>
       </c>
       <c r="O2" t="n">
-        <v>3.469221830368042</v>
+        <v>3.161730051040649</v>
       </c>
       <c r="P2" t="n">
-        <v>4.703635931015015</v>
+        <v>4.07926869392395</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-110605</t>
+          <t>20250714-154659</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2156,13 +2176,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -2172,7 +2194,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2184,50 +2206,50 @@
         <v>124</v>
       </c>
       <c r="C3" t="n">
-        <v>85.09903836250305</v>
+        <v>75.63354277610779</v>
       </c>
       <c r="D3" t="n">
-        <v>5.690000057220459</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8583333492279053</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8216666579246521</v>
+        <v>0.8149999976158142</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8183333277702332</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8083333373069763</v>
+        <v>0.8149999976158142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1105825460606044</v>
+        <v>0.1021522344240257</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0482885092496871</v>
+        <v>0.0478070527315139</v>
       </c>
       <c r="K3" t="n">
-        <v>20.43155384063721</v>
+        <v>18.66137671470642</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0296511125564575</v>
+        <v>0.0312884020805358</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0327609324455261</v>
+        <v>0.0357836771011352</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0440613293647766</v>
+        <v>0.0447394299507141</v>
       </c>
       <c r="O3" t="n">
-        <v>3.276093244552612</v>
+        <v>3.578367710113525</v>
       </c>
       <c r="P3" t="n">
-        <v>4.406132936477661</v>
+        <v>4.473942995071411</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-110846</t>
+          <t>20250714-154956</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -2272,13 +2294,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -2288,7 +2312,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2300,50 +2324,50 @@
         <v>189</v>
       </c>
       <c r="C4" t="n">
-        <v>128.0562715530396</v>
+        <v>111.7037491798401</v>
       </c>
       <c r="D4" t="n">
-        <v>5.690000057220459</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="E4" t="n">
         <v>0.8833333253860474</v>
       </c>
       <c r="F4" t="n">
-        <v>0.846666693687439</v>
+        <v>0.8433333039283752</v>
       </c>
       <c r="G4" t="n">
-        <v>0.846666693687439</v>
+        <v>0.8433333039283752</v>
       </c>
       <c r="H4" t="n">
         <v>0.8483333587646484</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1102857331907938</v>
+        <v>0.1028104233678686</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0458022989332675</v>
+        <v>0.043034590780735</v>
       </c>
       <c r="K4" t="n">
-        <v>20.6108136177063</v>
+        <v>19.01821827888489</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0263371443748474</v>
+        <v>0.0332936072349548</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0336103796958923</v>
+        <v>0.0314069008827209</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0430163311958313</v>
+        <v>0.0410171651840209</v>
       </c>
       <c r="O4" t="n">
-        <v>3.361037969589233</v>
+        <v>3.140690088272095</v>
       </c>
       <c r="P4" t="n">
-        <v>4.30163311958313</v>
+        <v>4.1017165184021</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-111121</t>
+          <t>20250714-155220</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2388,13 +2412,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2404,7 +2430,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2413,53 +2439,53 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="C5" t="n">
-        <v>85.95850110054016</v>
+        <v>106.9050788879394</v>
       </c>
       <c r="D5" t="n">
-        <v>5.690000057220459</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8500000238418579</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8399999737739563</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8366666436195374</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8149999976158142</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1087050251373948</v>
+        <v>0.1025802568017437</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0473263636231422</v>
+        <v>0.0427335649728775</v>
       </c>
       <c r="K5" t="n">
-        <v>21.26785778999329</v>
+        <v>18.92403078079224</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0251876330375671</v>
+        <v>0.033401288986206</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0329401493072509</v>
+        <v>0.0321153020858764</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0466545701026916</v>
+        <v>0.0410310816764831</v>
       </c>
       <c r="O5" t="n">
-        <v>3.294014930725098</v>
+        <v>3.211530208587646</v>
       </c>
       <c r="P5" t="n">
-        <v>4.665457010269165</v>
+        <v>4.103108167648315</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-111437</t>
+          <t>20250714-155521</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -2504,13 +2530,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2520,7 +2548,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2529,53 +2557,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="C6" t="n">
-        <v>111.1547703742981</v>
+        <v>66.10351467132568</v>
       </c>
       <c r="D6" t="n">
-        <v>5.690000057220459</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="E6" t="n">
-        <v>0.875</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8516666889190674</v>
+        <v>0.8133333325386047</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8500000238418579</v>
+        <v>0.8149999976158142</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8366666436195374</v>
+        <v>0.8050000071525574</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1084533712667662</v>
+        <v>0.1023389381963178</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0568149276077747</v>
+        <v>0.0425069518387317</v>
       </c>
       <c r="K6" t="n">
-        <v>20.60103440284729</v>
+        <v>18.75037717819214</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0266016292572021</v>
+        <v>0.0322875642776489</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0334083414077758</v>
+        <v>0.0315014028549194</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0431664586067199</v>
+        <v>0.0400184106826782</v>
       </c>
       <c r="O6" t="n">
-        <v>3.340834140777588</v>
+        <v>3.150140285491944</v>
       </c>
       <c r="P6" t="n">
-        <v>4.316645860671997</v>
+        <v>4.001841068267822</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-111712</t>
+          <t>20250714-155818</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -2620,13 +2648,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2636,7 +2666,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2806,53 +2836,53 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
-        <v>48.05517649650574</v>
+        <v>27.14626145362854</v>
       </c>
       <c r="D2" t="n">
         <v>2.289999961853028</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8833333253860474</v>
+        <v>0.875</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8483333587646484</v>
+        <v>0.8316666483879089</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8483333587646484</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8366666436195374</v>
+        <v>0.8133333325386047</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0600931783147314</v>
+        <v>0.0575709841766599</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0371667668223381</v>
+        <v>0.0263659004122018</v>
       </c>
       <c r="K2" t="n">
-        <v>8.634133577346802</v>
+        <v>7.563389539718628</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0122074198722839</v>
+        <v>0.0101862597465515</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02207612991333</v>
+        <v>0.0220785617828369</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0268963909149169</v>
+        <v>0.0293525791168212</v>
       </c>
       <c r="O2" t="n">
-        <v>2.207612991333008</v>
+        <v>2.207856178283691</v>
       </c>
       <c r="P2" t="n">
-        <v>2.689639091491699</v>
+        <v>2.935257911682129</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-120959</t>
+          <t>20250714-164735</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2897,13 +2927,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -2913,7 +2945,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2925,50 +2957,50 @@
         <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>28.4766800403595</v>
+        <v>25.27882814407349</v>
       </c>
       <c r="D3" t="n">
         <v>2.289999961853028</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8916666507720947</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8233333230018616</v>
+        <v>0.8149999976158142</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8133333325386047</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8149999976158142</v>
+        <v>0.7983333468437195</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0607664487842056</v>
+        <v>0.0570042686605894</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0341861359775066</v>
+        <v>0.0283454321324825</v>
       </c>
       <c r="K3" t="n">
-        <v>8.089501142501831</v>
+        <v>7.603069543838501</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0111751103401184</v>
+        <v>0.0105101680755615</v>
       </c>
       <c r="M3" t="n">
-        <v>0.022400517463684</v>
+        <v>0.0209878325462341</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0283977365493774</v>
+        <v>0.0286305546760559</v>
       </c>
       <c r="O3" t="n">
-        <v>2.240051746368408</v>
+        <v>2.098783254623413</v>
       </c>
       <c r="P3" t="n">
-        <v>2.839773654937744</v>
+        <v>2.863055467605591</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-121127</t>
+          <t>20250714-164838</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -3013,13 +3045,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -3029,7 +3063,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3038,53 +3072,53 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C4" t="n">
-        <v>35.97415208816528</v>
+        <v>34.42802739143372</v>
       </c>
       <c r="D4" t="n">
         <v>2.289999961853028</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8833333253860474</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8316666483879089</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8233333230018616</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8216666579246521</v>
       </c>
       <c r="I4" t="n">
-        <v>0.061910560597544</v>
+        <v>0.0581264926775081</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0262833777815103</v>
+        <v>0.028383407741785</v>
       </c>
       <c r="K4" t="n">
-        <v>7.938753604888916</v>
+        <v>7.519891500473022</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0138141894340515</v>
+        <v>0.0128072524070739</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0226953744888305</v>
+        <v>0.0212450385093688</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0298567652702331</v>
+        <v>0.0296578216552734</v>
       </c>
       <c r="O4" t="n">
-        <v>2.269537448883057</v>
+        <v>2.12450385093689</v>
       </c>
       <c r="P4" t="n">
-        <v>2.985676527023315</v>
+        <v>2.965782165527344</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-121234</t>
+          <t>20250714-164938</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -3129,13 +3163,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -3145,7 +3181,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3154,10 +3190,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C5" t="n">
-        <v>38.84278154373169</v>
+        <v>31.85383033752441</v>
       </c>
       <c r="D5" t="n">
         <v>2.289999961853028</v>
@@ -3166,41 +3202,41 @@
         <v>0.8916666507720947</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8450000286102295</v>
+        <v>0.8216666579246521</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8399999737739563</v>
+        <v>0.8199999928474426</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8316666483879089</v>
+        <v>0.8166666626930237</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0621739792562013</v>
+        <v>0.056162551747284</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0313461795449256</v>
+        <v>0.0287425145506858</v>
       </c>
       <c r="K5" t="n">
-        <v>8.743204355239868</v>
+        <v>7.794091701507568</v>
       </c>
       <c r="L5" t="n">
-        <v>0.015300908088684</v>
+        <v>0.0106668901443481</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0214247274398803</v>
+        <v>0.0221551632881164</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0311330389976501</v>
+        <v>0.0261896181106567</v>
       </c>
       <c r="O5" t="n">
-        <v>2.142472743988037</v>
+        <v>2.215516328811645</v>
       </c>
       <c r="P5" t="n">
-        <v>3.113303899765014</v>
+        <v>2.618961811065674</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-121349</t>
+          <t>20250714-165047</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -3245,13 +3281,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -3261,7 +3299,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3270,53 +3308,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C6" t="n">
-        <v>50.69442105293274</v>
+        <v>42.75549936294556</v>
       </c>
       <c r="D6" t="n">
         <v>2.289999961853028</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8833333253860474</v>
+        <v>0.9083333611488342</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8450000286102295</v>
+        <v>0.8349999785423279</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8433333039283752</v>
+        <v>0.82833331823349</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8366666436195374</v>
+        <v>0.8033333420753479</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0594174110076643</v>
+        <v>0.0572766175771012</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02955799177289</v>
+        <v>0.0285594556480646</v>
       </c>
       <c r="K6" t="n">
-        <v>7.988609552383423</v>
+        <v>7.696303129196167</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0118042516708374</v>
+        <v>0.0111970376968383</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0212696623802185</v>
+        <v>0.0218670988082885</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0301683640480041</v>
+        <v>0.0265065097808837</v>
       </c>
       <c r="O6" t="n">
-        <v>2.126966238021851</v>
+        <v>2.186709880828857</v>
       </c>
       <c r="P6" t="n">
-        <v>3.016836404800415</v>
+        <v>2.650650978088379</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-121508</t>
+          <t>20250714-165155</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -3361,13 +3399,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -3377,7 +3417,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
